--- a/grupos/6ARHM - Estadisticos 20222.xlsx
+++ b/grupos/6ARHM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="163">
   <si>
     <t>Materia</t>
   </si>
@@ -199,27 +199,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS DE LA SALUD</t>
-  </si>
-  <si>
-    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
-  </si>
-  <si>
-    <t>TEMAS DE FÍSICA</t>
-  </si>
-  <si>
-    <t>LITERATURA</t>
-  </si>
-  <si>
-    <t>INTRODUCCIÓN AL DERECHO</t>
-  </si>
-  <si>
-    <t>HISTORIA</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS SOCIALES</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>
@@ -6027,7 +6006,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
@@ -6067,13 +6046,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6081,19 +6060,28 @@
       <c r="E2">
         <v>0</v>
       </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
       <c r="I2">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -6101,293 +6089,144 @@
       <c r="E3">
         <v>0</v>
       </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
       <c r="I3">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>94.44</v>
+      </c>
+      <c r="G4">
+        <v>5.56</v>
+      </c>
+      <c r="H4">
+        <v>8.4</v>
       </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>97.22</v>
+      </c>
+      <c r="G5">
+        <v>2.78</v>
+      </c>
+      <c r="H5">
+        <v>9.1</v>
       </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>9.5</v>
+      </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>9.5</v>
+      </c>
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9">
-        <v>36</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>36</v>
-      </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10">
-        <v>36</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>36</v>
-      </c>
-      <c r="J10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11">
-        <v>36</v>
-      </c>
-      <c r="D11">
-        <v>34</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>94.44</v>
-      </c>
-      <c r="G11">
-        <v>5.56</v>
-      </c>
-      <c r="H11">
-        <v>8.4</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12">
-        <v>36</v>
-      </c>
-      <c r="D12">
-        <v>35</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>97.22</v>
-      </c>
-      <c r="G12">
-        <v>2.78</v>
-      </c>
-      <c r="H12">
-        <v>9.1</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13">
-        <v>36</v>
-      </c>
-      <c r="D13">
-        <v>36</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>100</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>9.5</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14">
-        <v>36</v>
-      </c>
-      <c r="D14">
-        <v>36</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>100</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>9.5</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
+      <c r="J7">
         <v>0</v>
       </c>
     </row>
@@ -6407,16 +6246,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6430,19 +6269,19 @@
         <v>20330051920368</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6450,19 +6289,19 @@
         <v>20330051920368</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6470,19 +6309,19 @@
         <v>20330051920156</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6490,19 +6329,19 @@
         <v>20330051920156</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6510,19 +6349,19 @@
         <v>20330051920157</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6530,19 +6369,19 @@
         <v>20330051920157</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6550,19 +6389,19 @@
         <v>20330051920158</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6570,19 +6409,19 @@
         <v>20330051920158</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6590,19 +6429,19 @@
         <v>20330051920369</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6610,19 +6449,19 @@
         <v>20330051920369</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6630,19 +6469,19 @@
         <v>20330051920160</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6650,19 +6489,19 @@
         <v>20330051920160</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6670,19 +6509,19 @@
         <v>20330051920161</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6690,19 +6529,19 @@
         <v>20330051920161</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6710,19 +6549,19 @@
         <v>20330051920162</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6730,19 +6569,19 @@
         <v>20330051920162</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -6750,19 +6589,19 @@
         <v>20330051920163</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -6770,19 +6609,19 @@
         <v>20330051920163</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -6790,19 +6629,19 @@
         <v>20330051920164</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -6810,19 +6649,19 @@
         <v>20330051920164</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -6830,19 +6669,19 @@
         <v>20330051920370</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -6850,19 +6689,19 @@
         <v>20330051920370</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -6870,19 +6709,19 @@
         <v>20330051920372</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -6890,19 +6729,19 @@
         <v>20330051920372</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -6910,19 +6749,19 @@
         <v>20330051920165</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -6930,19 +6769,19 @@
         <v>20330051920165</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E27" t="s">
         <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -6950,19 +6789,19 @@
         <v>20330051920167</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -6970,19 +6809,19 @@
         <v>20330051920167</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s">
         <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -6990,19 +6829,19 @@
         <v>20330051920166</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -7010,19 +6849,19 @@
         <v>20330051920166</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s">
         <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -7030,19 +6869,19 @@
         <v>20330051920371</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -7050,19 +6889,19 @@
         <v>20330051920371</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E33" t="s">
         <v>6</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -7070,19 +6909,19 @@
         <v>20330051920171</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -7090,19 +6929,19 @@
         <v>20330051920171</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E35" t="s">
         <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -7110,19 +6949,19 @@
         <v>20330051920172</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D36" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -7130,19 +6969,19 @@
         <v>20330051920172</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E37" t="s">
         <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -7150,19 +6989,19 @@
         <v>20330051920173</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D38" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -7170,19 +7009,19 @@
         <v>20330051920173</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D39" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E39" t="s">
         <v>6</v>
       </c>
       <c r="F39" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -7190,19 +7029,19 @@
         <v>20330051920174</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C40" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D40" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -7210,19 +7049,19 @@
         <v>20330051920174</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D41" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s">
         <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -7230,19 +7069,19 @@
         <v>20330051920306</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D42" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -7250,19 +7089,19 @@
         <v>20330051920306</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D43" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E43" t="s">
         <v>6</v>
       </c>
       <c r="F43" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -7270,19 +7109,19 @@
         <v>20330051920177</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D44" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -7290,19 +7129,19 @@
         <v>20330051920177</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D45" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E45" t="s">
         <v>6</v>
       </c>
       <c r="F45" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -7310,19 +7149,19 @@
         <v>20330051920178</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D46" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -7330,19 +7169,19 @@
         <v>20330051920178</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D47" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E47" t="s">
         <v>6</v>
       </c>
       <c r="F47" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -7350,19 +7189,19 @@
         <v>20330051920179</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D48" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -7370,19 +7209,19 @@
         <v>20330051920179</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C49" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D49" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E49" t="s">
         <v>6</v>
       </c>
       <c r="F49" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -7390,19 +7229,19 @@
         <v>20330051920180</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D50" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -7410,19 +7249,19 @@
         <v>20330051920180</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D51" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E51" t="s">
         <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -7430,19 +7269,19 @@
         <v>20330051920373</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C52" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D52" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -7450,19 +7289,19 @@
         <v>20330051920373</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D53" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E53" t="s">
         <v>6</v>
       </c>
       <c r="F53" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -7470,19 +7309,19 @@
         <v>20330051920145</v>
       </c>
       <c r="B54" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D54" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -7490,19 +7329,19 @@
         <v>20330051920145</v>
       </c>
       <c r="B55" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D55" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E55" t="s">
         <v>6</v>
       </c>
       <c r="F55" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -7510,19 +7349,19 @@
         <v>20330051920254</v>
       </c>
       <c r="B56" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D56" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -7530,19 +7369,19 @@
         <v>20330051920254</v>
       </c>
       <c r="B57" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C57" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D57" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E57" t="s">
         <v>6</v>
       </c>
       <c r="F57" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -7550,19 +7389,19 @@
         <v>20330051920181</v>
       </c>
       <c r="B58" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D58" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -7570,19 +7409,19 @@
         <v>20330051920181</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D59" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E59" t="s">
         <v>6</v>
       </c>
       <c r="F59" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -7590,19 +7429,19 @@
         <v>20330051920393</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C60" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D60" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -7610,19 +7449,19 @@
         <v>20330051920393</v>
       </c>
       <c r="B61" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C61" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D61" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E61" t="s">
         <v>6</v>
       </c>
       <c r="F61" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -7630,19 +7469,19 @@
         <v>20330051920182</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -7650,19 +7489,19 @@
         <v>20330051920182</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C63" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E63" t="s">
         <v>6</v>
       </c>
       <c r="F63" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -7670,19 +7509,19 @@
         <v>20330051920183</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C64" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -7690,19 +7529,19 @@
         <v>20330051920183</v>
       </c>
       <c r="B65" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C65" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D65" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E65" t="s">
         <v>6</v>
       </c>
       <c r="F65" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -7710,19 +7549,19 @@
         <v>20330051920184</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C66" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D66" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -7730,19 +7569,19 @@
         <v>20330051920184</v>
       </c>
       <c r="B67" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C67" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D67" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E67" t="s">
         <v>6</v>
       </c>
       <c r="F67" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -7750,19 +7589,19 @@
         <v>20330051920154</v>
       </c>
       <c r="B68" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C68" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D68" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -7770,19 +7609,19 @@
         <v>20330051920154</v>
       </c>
       <c r="B69" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C69" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D69" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
         <v>6</v>
       </c>
       <c r="F69" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -7790,19 +7629,19 @@
         <v>20330051920186</v>
       </c>
       <c r="B70" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C70" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D70" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -7810,19 +7649,19 @@
         <v>20330051920186</v>
       </c>
       <c r="B71" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C71" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D71" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E71" t="s">
         <v>6</v>
       </c>
       <c r="F71" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -7830,19 +7669,19 @@
         <v>20330051920388</v>
       </c>
       <c r="B72" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C72" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -7850,19 +7689,19 @@
         <v>20330051920388</v>
       </c>
       <c r="B73" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C73" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D73" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E73" t="s">
         <v>6</v>
       </c>
       <c r="F73" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -7881,16 +7720,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>58</v>
@@ -7901,13 +7740,13 @@
         <v>20330051920368</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -7918,13 +7757,13 @@
         <v>20330051920156</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -7935,13 +7774,13 @@
         <v>20330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -7952,13 +7791,13 @@
         <v>20330051920158</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -7969,13 +7808,13 @@
         <v>20330051920369</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -7986,13 +7825,13 @@
         <v>20330051920160</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -8003,13 +7842,13 @@
         <v>20330051920161</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -8020,13 +7859,13 @@
         <v>20330051920162</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -8037,13 +7876,13 @@
         <v>20330051920163</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -8054,13 +7893,13 @@
         <v>20330051920164</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -8071,13 +7910,13 @@
         <v>20330051920370</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -8088,13 +7927,13 @@
         <v>20330051920372</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -8105,13 +7944,13 @@
         <v>20330051920165</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -8122,13 +7961,13 @@
         <v>20330051920167</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -8139,13 +7978,13 @@
         <v>20330051920166</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -8156,13 +7995,13 @@
         <v>20330051920371</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -8173,13 +8012,13 @@
         <v>20330051920171</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -8190,13 +8029,13 @@
         <v>20330051920172</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -8207,13 +8046,13 @@
         <v>20330051920173</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -8224,13 +8063,13 @@
         <v>20330051920174</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -8241,13 +8080,13 @@
         <v>20330051920306</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -8258,13 +8097,13 @@
         <v>20330051920177</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E23">
         <v>2</v>
@@ -8275,13 +8114,13 @@
         <v>20330051920178</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -8292,13 +8131,13 @@
         <v>20330051920179</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E25">
         <v>2</v>
@@ -8309,13 +8148,13 @@
         <v>20330051920180</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E26">
         <v>2</v>
@@ -8326,13 +8165,13 @@
         <v>20330051920373</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -8343,13 +8182,13 @@
         <v>20330051920145</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -8360,13 +8199,13 @@
         <v>20330051920254</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -8377,13 +8216,13 @@
         <v>20330051920181</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -8394,13 +8233,13 @@
         <v>20330051920393</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E31">
         <v>2</v>
@@ -8411,13 +8250,13 @@
         <v>20330051920182</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E32">
         <v>2</v>
@@ -8428,13 +8267,13 @@
         <v>20330051920183</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E33">
         <v>2</v>
@@ -8445,13 +8284,13 @@
         <v>20330051920184</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -8462,13 +8301,13 @@
         <v>20330051920154</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E35">
         <v>2</v>
@@ -8479,13 +8318,13 @@
         <v>20330051920186</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D36" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -8496,13 +8335,13 @@
         <v>20330051920388</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E37">
         <v>2</v>
@@ -8524,16 +8363,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -8550,19 +8389,19 @@
         <v>20330051920368</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -8573,19 +8412,19 @@
         <v>20330051920368</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -8596,19 +8435,19 @@
         <v>20330051920156</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -8619,19 +8458,19 @@
         <v>20330051920156</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -8642,19 +8481,19 @@
         <v>20330051920157</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -8665,19 +8504,19 @@
         <v>20330051920157</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -8688,19 +8527,19 @@
         <v>20330051920158</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -8711,19 +8550,19 @@
         <v>20330051920158</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -8734,19 +8573,19 @@
         <v>20330051920369</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -8757,19 +8596,19 @@
         <v>20330051920369</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -8780,19 +8619,19 @@
         <v>20330051920160</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -8803,19 +8642,19 @@
         <v>20330051920160</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -8826,19 +8665,19 @@
         <v>20330051920161</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -8849,19 +8688,19 @@
         <v>20330051920161</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -8872,19 +8711,19 @@
         <v>20330051920162</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -8895,19 +8734,19 @@
         <v>20330051920162</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -8918,19 +8757,19 @@
         <v>20330051920163</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -8941,19 +8780,19 @@
         <v>20330051920163</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -8964,19 +8803,19 @@
         <v>20330051920164</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -8987,19 +8826,19 @@
         <v>20330051920164</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -9010,19 +8849,19 @@
         <v>20330051920370</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G22">
         <v>-1</v>
@@ -9033,19 +8872,19 @@
         <v>20330051920370</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -9056,19 +8895,19 @@
         <v>20330051920372</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G24">
         <v>-1</v>
@@ -9079,19 +8918,19 @@
         <v>20330051920372</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G25">
         <v>-1</v>
@@ -9102,19 +8941,19 @@
         <v>20330051920165</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G26">
         <v>-1</v>
@@ -9125,19 +8964,19 @@
         <v>20330051920165</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G27">
         <v>-1</v>
@@ -9148,19 +8987,19 @@
         <v>20330051920167</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G28">
         <v>-1</v>
@@ -9171,19 +9010,19 @@
         <v>20330051920167</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G29">
         <v>-1</v>
@@ -9194,19 +9033,19 @@
         <v>20330051920166</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E30" t="s">
         <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G30">
         <v>-1</v>
@@ -9217,19 +9056,19 @@
         <v>20330051920166</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G31">
         <v>-1</v>
@@ -9240,19 +9079,19 @@
         <v>20330051920371</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
       </c>
       <c r="F32" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G32">
         <v>-1</v>
@@ -9263,19 +9102,19 @@
         <v>20330051920371</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G33">
         <v>-1</v>
@@ -9286,19 +9125,19 @@
         <v>20330051920171</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E34" t="s">
         <v>6</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G34">
         <v>-1</v>
@@ -9309,19 +9148,19 @@
         <v>20330051920171</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G35">
         <v>-1</v>
@@ -9332,19 +9171,19 @@
         <v>20330051920173</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D36" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
         <v>6</v>
       </c>
       <c r="F36" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G36">
         <v>-1</v>
@@ -9355,19 +9194,19 @@
         <v>20330051920173</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G37">
         <v>-1</v>
@@ -9378,19 +9217,19 @@
         <v>20330051920306</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E38" t="s">
         <v>6</v>
       </c>
       <c r="F38" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G38">
         <v>-1</v>
@@ -9401,19 +9240,19 @@
         <v>20330051920306</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G39">
         <v>-1</v>
@@ -9424,19 +9263,19 @@
         <v>20330051920177</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D40" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E40" t="s">
         <v>6</v>
       </c>
       <c r="F40" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G40">
         <v>-1</v>
@@ -9447,19 +9286,19 @@
         <v>20330051920177</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G41">
         <v>-1</v>
@@ -9470,19 +9309,19 @@
         <v>20330051920179</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D42" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E42" t="s">
         <v>6</v>
       </c>
       <c r="F42" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G42">
         <v>-1</v>
@@ -9493,19 +9332,19 @@
         <v>20330051920179</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D43" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G43">
         <v>-1</v>
@@ -9516,19 +9355,19 @@
         <v>20330051920180</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C44" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D44" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E44" t="s">
         <v>6</v>
       </c>
       <c r="F44" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G44">
         <v>-1</v>
@@ -9539,19 +9378,19 @@
         <v>20330051920180</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C45" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D45" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G45">
         <v>-1</v>
@@ -9562,19 +9401,19 @@
         <v>20330051920373</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D46" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E46" t="s">
         <v>6</v>
       </c>
       <c r="F46" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G46">
         <v>-1</v>
@@ -9585,19 +9424,19 @@
         <v>20330051920373</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D47" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G47">
         <v>-1</v>
@@ -9608,19 +9447,19 @@
         <v>20330051920145</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D48" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E48" t="s">
         <v>6</v>
       </c>
       <c r="F48" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G48">
         <v>-1</v>
@@ -9631,19 +9470,19 @@
         <v>20330051920145</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D49" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G49">
         <v>-1</v>
@@ -9654,19 +9493,19 @@
         <v>20330051920254</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D50" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E50" t="s">
         <v>6</v>
       </c>
       <c r="F50" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G50">
         <v>-1</v>
@@ -9677,19 +9516,19 @@
         <v>20330051920254</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D51" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G51">
         <v>-1</v>
@@ -9700,19 +9539,19 @@
         <v>20330051920181</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D52" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E52" t="s">
         <v>6</v>
       </c>
       <c r="F52" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G52">
         <v>-1</v>
@@ -9723,19 +9562,19 @@
         <v>20330051920181</v>
       </c>
       <c r="B53" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C53" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D53" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G53">
         <v>-1</v>
@@ -9746,19 +9585,19 @@
         <v>20330051920393</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D54" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E54" t="s">
         <v>6</v>
       </c>
       <c r="F54" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G54">
         <v>-1</v>
@@ -9769,19 +9608,19 @@
         <v>20330051920393</v>
       </c>
       <c r="B55" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D55" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G55">
         <v>-1</v>
@@ -9792,19 +9631,19 @@
         <v>20330051920182</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C56" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D56" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E56" t="s">
         <v>6</v>
       </c>
       <c r="F56" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G56">
         <v>-1</v>
@@ -9815,19 +9654,19 @@
         <v>20330051920182</v>
       </c>
       <c r="B57" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C57" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G57">
         <v>-1</v>
@@ -9838,19 +9677,19 @@
         <v>20330051920183</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C58" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D58" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E58" t="s">
         <v>6</v>
       </c>
       <c r="F58" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G58">
         <v>-1</v>
@@ -9861,19 +9700,19 @@
         <v>20330051920183</v>
       </c>
       <c r="B59" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C59" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G59">
         <v>-1</v>
@@ -9884,19 +9723,19 @@
         <v>20330051920184</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C60" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D60" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E60" t="s">
         <v>6</v>
       </c>
       <c r="F60" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G60">
         <v>-1</v>
@@ -9907,19 +9746,19 @@
         <v>20330051920184</v>
       </c>
       <c r="B61" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C61" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D61" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G61">
         <v>-1</v>
@@ -9930,19 +9769,19 @@
         <v>20330051920154</v>
       </c>
       <c r="B62" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C62" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D62" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E62" t="s">
         <v>6</v>
       </c>
       <c r="F62" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G62">
         <v>-1</v>
@@ -9953,19 +9792,19 @@
         <v>20330051920154</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D63" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G63">
         <v>-1</v>
@@ -9976,19 +9815,19 @@
         <v>20330051920186</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C64" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E64" t="s">
         <v>6</v>
       </c>
       <c r="F64" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G64">
         <v>-1</v>
@@ -9999,19 +9838,19 @@
         <v>20330051920186</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C65" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D65" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G65">
         <v>-1</v>
@@ -10022,19 +9861,19 @@
         <v>20330051920388</v>
       </c>
       <c r="B66" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C66" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D66" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E66" t="s">
         <v>6</v>
       </c>
       <c r="F66" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G66">
         <v>-1</v>
@@ -10045,19 +9884,19 @@
         <v>20330051920388</v>
       </c>
       <c r="B67" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C67" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D67" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G67">
         <v>-1</v>

--- a/grupos/6ARHM - Estadisticos 20222.xlsx
+++ b/grupos/6ARHM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="163">
   <si>
     <t>Materia</t>
   </si>
@@ -1002,7 +1002,7 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -1056,7 +1056,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>9</v>
@@ -1133,7 +1133,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -1156,7 +1156,7 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -1210,7 +1210,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1233,7 +1233,7 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -1310,7 +1310,7 @@
         <v>9</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F8">
         <v>9</v>
@@ -1364,7 +1364,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1387,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F9">
         <v>9</v>
@@ -1441,7 +1441,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1464,7 +1464,7 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1518,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1541,7 +1541,7 @@
         <v>10</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1595,7 +1595,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1618,7 +1618,7 @@
         <v>10</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -1672,7 +1672,7 @@
         <v>10</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1695,7 +1695,7 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F13">
         <v>9</v>
@@ -1749,7 +1749,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1772,7 +1772,7 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F14">
         <v>10</v>
@@ -1826,7 +1826,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1849,7 +1849,7 @@
         <v>9</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>9</v>
@@ -1903,7 +1903,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1926,7 +1926,7 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -1980,7 +1980,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -2003,7 +2003,7 @@
         <v>10</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F17">
         <v>10</v>
@@ -2057,7 +2057,7 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -2080,7 +2080,7 @@
         <v>9</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>9</v>
@@ -2134,7 +2134,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2157,7 +2157,7 @@
         <v>10</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F19">
         <v>10</v>
@@ -2211,7 +2211,7 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -2234,7 +2234,7 @@
         <v>10</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -2288,7 +2288,7 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2311,7 +2311,7 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>9</v>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2388,7 +2388,7 @@
         <v>10</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -2442,7 +2442,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2465,7 +2465,7 @@
         <v>10</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -2519,7 +2519,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2542,7 +2542,7 @@
         <v>9</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F24">
         <v>9</v>
@@ -2596,7 +2596,7 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2619,7 +2619,7 @@
         <v>10</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -2673,7 +2673,7 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2696,7 +2696,7 @@
         <v>9</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F26">
         <v>9</v>
@@ -2750,7 +2750,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2773,7 +2773,7 @@
         <v>10</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F27">
         <v>10</v>
@@ -2827,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2850,7 +2850,7 @@
         <v>9</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F28">
         <v>9</v>
@@ -2904,7 +2904,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2927,7 +2927,7 @@
         <v>9</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F29">
         <v>9</v>
@@ -2981,7 +2981,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3004,7 +3004,7 @@
         <v>9</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>9</v>
@@ -3058,7 +3058,7 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -3081,7 +3081,7 @@
         <v>9</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F31">
         <v>9</v>
@@ -3135,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -3158,7 +3158,7 @@
         <v>10</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>10</v>
@@ -3212,7 +3212,7 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3235,7 +3235,7 @@
         <v>10</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>10</v>
@@ -3289,7 +3289,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3312,7 +3312,7 @@
         <v>10</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F34">
         <v>10</v>
@@ -3366,7 +3366,7 @@
         <v>10</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3389,7 +3389,7 @@
         <v>9</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F35">
         <v>9</v>
@@ -3443,7 +3443,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3466,7 +3466,7 @@
         <v>10</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F36">
         <v>10</v>
@@ -3520,7 +3520,7 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3543,7 +3543,7 @@
         <v>10</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F37">
         <v>10</v>
@@ -3597,7 +3597,7 @@
         <v>10</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3620,7 +3620,7 @@
         <v>9</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F38">
         <v>9</v>
@@ -3674,7 +3674,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>9</v>
@@ -3697,7 +3697,7 @@
         <v>9</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F39">
         <v>9</v>
@@ -3751,7 +3751,7 @@
         <v>9</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>9</v>
@@ -3884,7 +3884,7 @@
         <v>132</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>132</v>
@@ -3943,7 +3943,7 @@
         <v>132</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>132</v>
@@ -4002,7 +4002,7 @@
         <v>132</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F6">
         <v>132</v>
@@ -4061,7 +4061,7 @@
         <v>132</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>132</v>
@@ -4120,7 +4120,7 @@
         <v>132</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>132</v>
@@ -4179,7 +4179,7 @@
         <v>132</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>132</v>
@@ -4238,7 +4238,7 @@
         <v>132</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>132</v>
@@ -4297,7 +4297,7 @@
         <v>132</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>132</v>
@@ -4356,7 +4356,7 @@
         <v>132</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>132</v>
@@ -4415,7 +4415,7 @@
         <v>132</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>132</v>
@@ -4474,7 +4474,7 @@
         <v>132</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>132</v>
@@ -4533,7 +4533,7 @@
         <v>132</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>132</v>
@@ -4592,7 +4592,7 @@
         <v>132</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>132</v>
@@ -4651,7 +4651,7 @@
         <v>132</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>132</v>
@@ -4710,7 +4710,7 @@
         <v>132</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>132</v>
@@ -4769,7 +4769,7 @@
         <v>132</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>132</v>
@@ -4828,7 +4828,7 @@
         <v>132</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>132</v>
@@ -4887,7 +4887,7 @@
         <v>128</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F21">
         <v>128</v>
@@ -4946,7 +4946,7 @@
         <v>132</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>132</v>
@@ -5005,7 +5005,7 @@
         <v>132</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F23">
         <v>132</v>
@@ -5064,7 +5064,7 @@
         <v>132</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>132</v>
@@ -5123,7 +5123,7 @@
         <v>132</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>132</v>
@@ -5182,7 +5182,7 @@
         <v>132</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>132</v>
@@ -5241,7 +5241,7 @@
         <v>132</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>132</v>
@@ -5300,7 +5300,7 @@
         <v>132</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>132</v>
@@ -5359,7 +5359,7 @@
         <v>132</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>132</v>
@@ -5418,7 +5418,7 @@
         <v>132</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>132</v>
@@ -5477,7 +5477,7 @@
         <v>132</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>132</v>
@@ -5536,7 +5536,7 @@
         <v>132</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>132</v>
@@ -5595,7 +5595,7 @@
         <v>132</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>132</v>
@@ -5654,7 +5654,7 @@
         <v>132</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>132</v>
@@ -5713,7 +5713,7 @@
         <v>132</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>132</v>
@@ -5772,7 +5772,7 @@
         <v>132</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F36">
         <v>132</v>
@@ -5831,7 +5831,7 @@
         <v>132</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37">
         <v>132</v>
@@ -5890,7 +5890,7 @@
         <v>124</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F38">
         <v>124</v>
@@ -5949,7 +5949,7 @@
         <v>132</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39">
         <v>132</v>
@@ -6046,7 +6046,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -6075,7 +6075,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -6084,22 +6084,25 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>16.67</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6237,7 +6240,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6278,7 +6281,7 @@
         <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>60</v>
@@ -6286,16 +6289,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920368</v>
+        <v>20330051920156</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -6306,19 +6309,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920156</v>
+        <v>20330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>60</v>
@@ -6326,16 +6329,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920156</v>
+        <v>20330051920158</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -6346,19 +6349,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920157</v>
+        <v>20330051920369</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>60</v>
@@ -6366,16 +6369,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920157</v>
+        <v>20330051920160</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -6386,19 +6389,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920158</v>
+        <v>20330051920161</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>60</v>
@@ -6406,16 +6409,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920158</v>
+        <v>20330051920162</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -6426,19 +6429,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920369</v>
+        <v>20330051920163</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>60</v>
@@ -6446,16 +6449,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920369</v>
+        <v>20330051920164</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -6466,19 +6469,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920160</v>
+        <v>20330051920370</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>60</v>
@@ -6486,16 +6489,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920160</v>
+        <v>20330051920372</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -6506,19 +6509,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920161</v>
+        <v>20330051920165</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>60</v>
@@ -6526,16 +6529,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920161</v>
+        <v>20330051920167</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -6546,19 +6549,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920162</v>
+        <v>20330051920166</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
         <v>60</v>
@@ -6566,16 +6569,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920162</v>
+        <v>20330051920371</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -6586,19 +6589,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920163</v>
+        <v>20330051920171</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>60</v>
@@ -6606,16 +6609,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920163</v>
+        <v>20330051920172</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -6626,19 +6629,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920164</v>
+        <v>20330051920173</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
         <v>60</v>
@@ -6646,16 +6649,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920164</v>
+        <v>20330051920174</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
         <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
@@ -6666,19 +6669,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920370</v>
+        <v>20330051920306</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
         <v>60</v>
@@ -6686,16 +6689,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920370</v>
+        <v>20330051920177</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -6706,19 +6709,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920372</v>
+        <v>20330051920178</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
         <v>60</v>
@@ -6726,16 +6729,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920372</v>
+        <v>20330051920179</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
@@ -6746,19 +6749,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920165</v>
+        <v>20330051920180</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
         <v>60</v>
@@ -6766,16 +6769,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920165</v>
+        <v>20330051920373</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="E27" t="s">
         <v>6</v>
@@ -6786,19 +6789,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920167</v>
+        <v>20330051920145</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F28" t="s">
         <v>60</v>
@@ -6806,16 +6809,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920167</v>
+        <v>20330051920254</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E29" t="s">
         <v>6</v>
@@ -6826,19 +6829,19 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920166</v>
+        <v>20330051920181</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
         <v>60</v>
@@ -6846,16 +6849,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920166</v>
+        <v>20330051920393</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="E31" t="s">
         <v>6</v>
@@ -6866,19 +6869,19 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920371</v>
+        <v>20330051920182</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
         <v>60</v>
@@ -6886,16 +6889,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920371</v>
+        <v>20330051920183</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E33" t="s">
         <v>6</v>
@@ -6906,19 +6909,19 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920171</v>
+        <v>20330051920184</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F34" t="s">
         <v>60</v>
@@ -6926,16 +6929,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920171</v>
+        <v>20330051920154</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="E35" t="s">
         <v>6</v>
@@ -6946,19 +6949,19 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920172</v>
+        <v>20330051920186</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="D36" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F36" t="s">
         <v>60</v>
@@ -6966,741 +6969,21 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920172</v>
+        <v>20330051920388</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="E37" t="s">
         <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920173</v>
-      </c>
-      <c r="B38" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920173</v>
-      </c>
-      <c r="B39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" t="s">
-        <v>115</v>
-      </c>
-      <c r="D39" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920174</v>
-      </c>
-      <c r="B40" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" t="s">
-        <v>108</v>
-      </c>
-      <c r="D40" t="s">
-        <v>146</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920174</v>
-      </c>
-      <c r="B41" t="s">
-        <v>86</v>
-      </c>
-      <c r="C41" t="s">
-        <v>108</v>
-      </c>
-      <c r="D41" t="s">
-        <v>146</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920306</v>
-      </c>
-      <c r="B42" t="s">
-        <v>87</v>
-      </c>
-      <c r="C42" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" t="s">
-        <v>147</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920306</v>
-      </c>
-      <c r="B43" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" t="s">
-        <v>78</v>
-      </c>
-      <c r="D43" t="s">
-        <v>147</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920177</v>
-      </c>
-      <c r="B44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44" t="s">
-        <v>148</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920177</v>
-      </c>
-      <c r="B45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" t="s">
-        <v>116</v>
-      </c>
-      <c r="D45" t="s">
-        <v>148</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920178</v>
-      </c>
-      <c r="B46" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" t="s">
-        <v>117</v>
-      </c>
-      <c r="D46" t="s">
-        <v>149</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920178</v>
-      </c>
-      <c r="B47" t="s">
-        <v>89</v>
-      </c>
-      <c r="C47" t="s">
-        <v>117</v>
-      </c>
-      <c r="D47" t="s">
-        <v>149</v>
-      </c>
-      <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920179</v>
-      </c>
-      <c r="B48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" t="s">
-        <v>118</v>
-      </c>
-      <c r="D48" t="s">
-        <v>150</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920179</v>
-      </c>
-      <c r="B49" t="s">
-        <v>90</v>
-      </c>
-      <c r="C49" t="s">
-        <v>118</v>
-      </c>
-      <c r="D49" t="s">
-        <v>150</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920180</v>
-      </c>
-      <c r="B50" t="s">
-        <v>91</v>
-      </c>
-      <c r="C50" t="s">
-        <v>119</v>
-      </c>
-      <c r="D50" t="s">
-        <v>151</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920180</v>
-      </c>
-      <c r="B51" t="s">
-        <v>91</v>
-      </c>
-      <c r="C51" t="s">
-        <v>119</v>
-      </c>
-      <c r="D51" t="s">
-        <v>151</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920373</v>
-      </c>
-      <c r="B52" t="s">
-        <v>92</v>
-      </c>
-      <c r="C52" t="s">
-        <v>71</v>
-      </c>
-      <c r="D52" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920373</v>
-      </c>
-      <c r="B53" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" t="s">
-        <v>71</v>
-      </c>
-      <c r="D53" t="s">
-        <v>152</v>
-      </c>
-      <c r="E53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920145</v>
-      </c>
-      <c r="B54" t="s">
-        <v>93</v>
-      </c>
-      <c r="C54" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" t="s">
-        <v>153</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920145</v>
-      </c>
-      <c r="B55" t="s">
-        <v>93</v>
-      </c>
-      <c r="C55" t="s">
-        <v>108</v>
-      </c>
-      <c r="D55" t="s">
-        <v>153</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920254</v>
-      </c>
-      <c r="B56" t="s">
-        <v>94</v>
-      </c>
-      <c r="C56" t="s">
-        <v>120</v>
-      </c>
-      <c r="D56" t="s">
-        <v>154</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920254</v>
-      </c>
-      <c r="B57" t="s">
-        <v>94</v>
-      </c>
-      <c r="C57" t="s">
-        <v>120</v>
-      </c>
-      <c r="D57" t="s">
-        <v>154</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920181</v>
-      </c>
-      <c r="B58" t="s">
-        <v>94</v>
-      </c>
-      <c r="C58" t="s">
-        <v>115</v>
-      </c>
-      <c r="D58" t="s">
-        <v>155</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920181</v>
-      </c>
-      <c r="B59" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" t="s">
-        <v>115</v>
-      </c>
-      <c r="D59" t="s">
-        <v>155</v>
-      </c>
-      <c r="E59" t="s">
-        <v>6</v>
-      </c>
-      <c r="F59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920393</v>
-      </c>
-      <c r="B60" t="s">
-        <v>95</v>
-      </c>
-      <c r="C60" t="s">
-        <v>121</v>
-      </c>
-      <c r="D60" t="s">
-        <v>156</v>
-      </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920393</v>
-      </c>
-      <c r="B61" t="s">
-        <v>95</v>
-      </c>
-      <c r="C61" t="s">
-        <v>121</v>
-      </c>
-      <c r="D61" t="s">
-        <v>156</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920182</v>
-      </c>
-      <c r="B62" t="s">
-        <v>96</v>
-      </c>
-      <c r="C62" t="s">
-        <v>122</v>
-      </c>
-      <c r="D62" t="s">
-        <v>157</v>
-      </c>
-      <c r="E62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920182</v>
-      </c>
-      <c r="B63" t="s">
-        <v>96</v>
-      </c>
-      <c r="C63" t="s">
-        <v>122</v>
-      </c>
-      <c r="D63" t="s">
-        <v>157</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920183</v>
-      </c>
-      <c r="B64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C64" t="s">
-        <v>123</v>
-      </c>
-      <c r="D64" t="s">
-        <v>158</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920183</v>
-      </c>
-      <c r="B65" t="s">
-        <v>97</v>
-      </c>
-      <c r="C65" t="s">
-        <v>123</v>
-      </c>
-      <c r="D65" t="s">
-        <v>158</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920184</v>
-      </c>
-      <c r="B66" t="s">
-        <v>97</v>
-      </c>
-      <c r="C66" t="s">
-        <v>124</v>
-      </c>
-      <c r="D66" t="s">
-        <v>159</v>
-      </c>
-      <c r="E66" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920184</v>
-      </c>
-      <c r="B67" t="s">
-        <v>97</v>
-      </c>
-      <c r="C67" t="s">
-        <v>124</v>
-      </c>
-      <c r="D67" t="s">
-        <v>159</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>20330051920154</v>
-      </c>
-      <c r="B68" t="s">
-        <v>98</v>
-      </c>
-      <c r="C68" t="s">
-        <v>75</v>
-      </c>
-      <c r="D68" t="s">
-        <v>160</v>
-      </c>
-      <c r="E68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>20330051920154</v>
-      </c>
-      <c r="B69" t="s">
-        <v>98</v>
-      </c>
-      <c r="C69" t="s">
-        <v>75</v>
-      </c>
-      <c r="D69" t="s">
-        <v>160</v>
-      </c>
-      <c r="E69" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>20330051920186</v>
-      </c>
-      <c r="B70" t="s">
-        <v>99</v>
-      </c>
-      <c r="C70" t="s">
-        <v>125</v>
-      </c>
-      <c r="D70" t="s">
-        <v>161</v>
-      </c>
-      <c r="E70" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920186</v>
-      </c>
-      <c r="B71" t="s">
-        <v>99</v>
-      </c>
-      <c r="C71" t="s">
-        <v>125</v>
-      </c>
-      <c r="D71" t="s">
-        <v>161</v>
-      </c>
-      <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920388</v>
-      </c>
-      <c r="B72" t="s">
-        <v>100</v>
-      </c>
-      <c r="C72" t="s">
-        <v>126</v>
-      </c>
-      <c r="D72" t="s">
-        <v>162</v>
-      </c>
-      <c r="E72" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920388</v>
-      </c>
-      <c r="B73" t="s">
-        <v>100</v>
-      </c>
-      <c r="C73" t="s">
-        <v>126</v>
-      </c>
-      <c r="D73" t="s">
-        <v>162</v>
-      </c>
-      <c r="E73" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" t="s">
         <v>60</v>
       </c>
     </row>
@@ -7749,7 +7032,7 @@
         <v>127</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7766,7 +7049,7 @@
         <v>128</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7783,7 +7066,7 @@
         <v>129</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7800,7 +7083,7 @@
         <v>130</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7817,7 +7100,7 @@
         <v>131</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7834,7 +7117,7 @@
         <v>132</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7851,7 +7134,7 @@
         <v>133</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7868,7 +7151,7 @@
         <v>134</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7885,7 +7168,7 @@
         <v>135</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7902,7 +7185,7 @@
         <v>136</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7919,7 +7202,7 @@
         <v>137</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7936,7 +7219,7 @@
         <v>138</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7953,7 +7236,7 @@
         <v>139</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7970,7 +7253,7 @@
         <v>140</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7987,7 +7270,7 @@
         <v>141</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8004,7 +7287,7 @@
         <v>142</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8021,7 +7304,7 @@
         <v>143</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8038,7 +7321,7 @@
         <v>144</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8055,7 +7338,7 @@
         <v>145</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8072,7 +7355,7 @@
         <v>146</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8089,7 +7372,7 @@
         <v>147</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8106,7 +7389,7 @@
         <v>148</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8123,7 +7406,7 @@
         <v>149</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8140,7 +7423,7 @@
         <v>150</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8157,7 +7440,7 @@
         <v>151</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8174,7 +7457,7 @@
         <v>152</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8191,7 +7474,7 @@
         <v>153</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8208,7 +7491,7 @@
         <v>154</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8225,7 +7508,7 @@
         <v>155</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8242,7 +7525,7 @@
         <v>156</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8259,7 +7542,7 @@
         <v>157</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8276,7 +7559,7 @@
         <v>158</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8293,7 +7576,7 @@
         <v>159</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8310,7 +7593,7 @@
         <v>160</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8327,7 +7610,7 @@
         <v>161</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8344,7 +7627,7 @@
         <v>162</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8354,7 +7637,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8386,16 +7669,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920368</v>
+        <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -8409,16 +7692,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920368</v>
+        <v>20330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -8427,21 +7710,21 @@
         <v>60</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920156</v>
+        <v>20330051920162</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -8455,16 +7738,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920156</v>
+        <v>20330051920162</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -8473,21 +7756,21 @@
         <v>60</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920157</v>
+        <v>20330051920182</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -8501,16 +7784,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920157</v>
+        <v>20330051920182</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -8519,21 +7802,21 @@
         <v>60</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920158</v>
+        <v>20330051920368</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -8547,19 +7830,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920158</v>
+        <v>20330051920156</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>60</v>
@@ -8570,16 +7853,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920369</v>
+        <v>20330051920158</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -8605,7 +7888,7 @@
         <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>60</v>
@@ -8639,19 +7922,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920160</v>
+        <v>20330051920161</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>60</v>
@@ -8662,16 +7945,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920161</v>
+        <v>20330051920163</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -8685,19 +7968,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920161</v>
+        <v>20330051920164</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>60</v>
@@ -8708,16 +7991,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920162</v>
+        <v>20330051920370</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -8731,19 +8014,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920162</v>
+        <v>20330051920372</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
         <v>60</v>
@@ -8754,16 +8037,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920163</v>
+        <v>20330051920165</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
@@ -8777,19 +8060,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920163</v>
+        <v>20330051920167</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
         <v>60</v>
@@ -8800,16 +8083,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920164</v>
+        <v>20330051920166</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -8823,19 +8106,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920164</v>
+        <v>20330051920371</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
         <v>60</v>
@@ -8846,16 +8129,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920370</v>
+        <v>20330051920171</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -8869,19 +8152,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920370</v>
+        <v>20330051920173</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
         <v>60</v>
@@ -8892,16 +8175,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920372</v>
+        <v>20330051920306</v>
       </c>
       <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
         <v>78</v>
       </c>
-      <c r="C24" t="s">
-        <v>110</v>
-      </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
@@ -8915,19 +8198,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920372</v>
+        <v>20330051920177</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
         <v>60</v>
@@ -8938,16 +8221,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920165</v>
+        <v>20330051920179</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
@@ -8961,19 +8244,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920165</v>
+        <v>20330051920180</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
         <v>60</v>
@@ -8984,16 +8267,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920167</v>
+        <v>20330051920373</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
@@ -9007,19 +8290,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920167</v>
+        <v>20330051920145</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
         <v>60</v>
@@ -9030,16 +8313,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920166</v>
+        <v>20330051920254</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="E30" t="s">
         <v>6</v>
@@ -9053,19 +8336,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920166</v>
+        <v>20330051920181</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
         <v>60</v>
@@ -9076,16 +8359,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920371</v>
+        <v>20330051920393</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
@@ -9099,19 +8382,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920371</v>
+        <v>20330051920183</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
         <v>60</v>
@@ -9122,16 +8405,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920171</v>
+        <v>20330051920184</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="E34" t="s">
         <v>6</v>
@@ -9145,19 +8428,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920171</v>
+        <v>20330051920154</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
         <v>60</v>
@@ -9168,16 +8451,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920173</v>
+        <v>20330051920186</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E36" t="s">
         <v>6</v>
@@ -9191,714 +8474,24 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920173</v>
+        <v>20330051920388</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F37" t="s">
         <v>60</v>
       </c>
       <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>20330051920306</v>
-      </c>
-      <c r="B38" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" t="s">
-        <v>147</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>20330051920306</v>
-      </c>
-      <c r="B39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39" t="s">
-        <v>147</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>20330051920177</v>
-      </c>
-      <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" t="s">
-        <v>116</v>
-      </c>
-      <c r="D40" t="s">
-        <v>148</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>60</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>20330051920177</v>
-      </c>
-      <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41" t="s">
-        <v>148</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>20330051920179</v>
-      </c>
-      <c r="B42" t="s">
-        <v>90</v>
-      </c>
-      <c r="C42" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" t="s">
-        <v>150</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>60</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>20330051920179</v>
-      </c>
-      <c r="B43" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" t="s">
-        <v>150</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>60</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>20330051920180</v>
-      </c>
-      <c r="B44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" t="s">
-        <v>151</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>20330051920180</v>
-      </c>
-      <c r="B45" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" t="s">
-        <v>119</v>
-      </c>
-      <c r="D45" t="s">
-        <v>151</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>60</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>20330051920373</v>
-      </c>
-      <c r="B46" t="s">
-        <v>92</v>
-      </c>
-      <c r="C46" t="s">
-        <v>71</v>
-      </c>
-      <c r="D46" t="s">
-        <v>152</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>60</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>20330051920373</v>
-      </c>
-      <c r="B47" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" t="s">
-        <v>71</v>
-      </c>
-      <c r="D47" t="s">
-        <v>152</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>60</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>20330051920145</v>
-      </c>
-      <c r="B48" t="s">
-        <v>93</v>
-      </c>
-      <c r="C48" t="s">
-        <v>108</v>
-      </c>
-      <c r="D48" t="s">
-        <v>153</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>60</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>20330051920145</v>
-      </c>
-      <c r="B49" t="s">
-        <v>93</v>
-      </c>
-      <c r="C49" t="s">
-        <v>108</v>
-      </c>
-      <c r="D49" t="s">
-        <v>153</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>60</v>
-      </c>
-      <c r="G49">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>20330051920254</v>
-      </c>
-      <c r="B50" t="s">
-        <v>94</v>
-      </c>
-      <c r="C50" t="s">
-        <v>120</v>
-      </c>
-      <c r="D50" t="s">
-        <v>154</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>60</v>
-      </c>
-      <c r="G50">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>20330051920254</v>
-      </c>
-      <c r="B51" t="s">
-        <v>94</v>
-      </c>
-      <c r="C51" t="s">
-        <v>120</v>
-      </c>
-      <c r="D51" t="s">
-        <v>154</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-      <c r="G51">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>20330051920181</v>
-      </c>
-      <c r="B52" t="s">
-        <v>94</v>
-      </c>
-      <c r="C52" t="s">
-        <v>115</v>
-      </c>
-      <c r="D52" t="s">
-        <v>155</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>60</v>
-      </c>
-      <c r="G52">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>20330051920181</v>
-      </c>
-      <c r="B53" t="s">
-        <v>94</v>
-      </c>
-      <c r="C53" t="s">
-        <v>115</v>
-      </c>
-      <c r="D53" t="s">
-        <v>155</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>60</v>
-      </c>
-      <c r="G53">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>20330051920393</v>
-      </c>
-      <c r="B54" t="s">
-        <v>95</v>
-      </c>
-      <c r="C54" t="s">
-        <v>121</v>
-      </c>
-      <c r="D54" t="s">
-        <v>156</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>60</v>
-      </c>
-      <c r="G54">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>20330051920393</v>
-      </c>
-      <c r="B55" t="s">
-        <v>95</v>
-      </c>
-      <c r="C55" t="s">
-        <v>121</v>
-      </c>
-      <c r="D55" t="s">
-        <v>156</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>60</v>
-      </c>
-      <c r="G55">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>20330051920182</v>
-      </c>
-      <c r="B56" t="s">
-        <v>96</v>
-      </c>
-      <c r="C56" t="s">
-        <v>122</v>
-      </c>
-      <c r="D56" t="s">
-        <v>157</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>60</v>
-      </c>
-      <c r="G56">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
-        <v>20330051920182</v>
-      </c>
-      <c r="B57" t="s">
-        <v>96</v>
-      </c>
-      <c r="C57" t="s">
-        <v>122</v>
-      </c>
-      <c r="D57" t="s">
-        <v>157</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>60</v>
-      </c>
-      <c r="G57">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58">
-        <v>20330051920183</v>
-      </c>
-      <c r="B58" t="s">
-        <v>97</v>
-      </c>
-      <c r="C58" t="s">
-        <v>123</v>
-      </c>
-      <c r="D58" t="s">
-        <v>158</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>60</v>
-      </c>
-      <c r="G58">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
-        <v>20330051920183</v>
-      </c>
-      <c r="B59" t="s">
-        <v>97</v>
-      </c>
-      <c r="C59" t="s">
-        <v>123</v>
-      </c>
-      <c r="D59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>60</v>
-      </c>
-      <c r="G59">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60">
-        <v>20330051920184</v>
-      </c>
-      <c r="B60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C60" t="s">
-        <v>124</v>
-      </c>
-      <c r="D60" t="s">
-        <v>159</v>
-      </c>
-      <c r="E60" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" t="s">
-        <v>60</v>
-      </c>
-      <c r="G60">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61">
-        <v>20330051920184</v>
-      </c>
-      <c r="B61" t="s">
-        <v>97</v>
-      </c>
-      <c r="C61" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" t="s">
-        <v>159</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>60</v>
-      </c>
-      <c r="G61">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62">
-        <v>20330051920154</v>
-      </c>
-      <c r="B62" t="s">
-        <v>98</v>
-      </c>
-      <c r="C62" t="s">
-        <v>75</v>
-      </c>
-      <c r="D62" t="s">
-        <v>160</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>60</v>
-      </c>
-      <c r="G62">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63">
-        <v>20330051920154</v>
-      </c>
-      <c r="B63" t="s">
-        <v>98</v>
-      </c>
-      <c r="C63" t="s">
-        <v>75</v>
-      </c>
-      <c r="D63" t="s">
-        <v>160</v>
-      </c>
-      <c r="E63" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" t="s">
-        <v>60</v>
-      </c>
-      <c r="G63">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64">
-        <v>20330051920186</v>
-      </c>
-      <c r="B64" t="s">
-        <v>99</v>
-      </c>
-      <c r="C64" t="s">
-        <v>125</v>
-      </c>
-      <c r="D64" t="s">
-        <v>161</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>60</v>
-      </c>
-      <c r="G64">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65">
-        <v>20330051920186</v>
-      </c>
-      <c r="B65" t="s">
-        <v>99</v>
-      </c>
-      <c r="C65" t="s">
-        <v>125</v>
-      </c>
-      <c r="D65" t="s">
-        <v>161</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>60</v>
-      </c>
-      <c r="G65">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66">
-        <v>20330051920388</v>
-      </c>
-      <c r="B66" t="s">
-        <v>100</v>
-      </c>
-      <c r="C66" t="s">
-        <v>126</v>
-      </c>
-      <c r="D66" t="s">
-        <v>162</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>60</v>
-      </c>
-      <c r="G66">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67">
-        <v>20330051920388</v>
-      </c>
-      <c r="B67" t="s">
-        <v>100</v>
-      </c>
-      <c r="C67" t="s">
-        <v>126</v>
-      </c>
-      <c r="D67" t="s">
-        <v>162</v>
-      </c>
-      <c r="E67" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" t="s">
-        <v>60</v>
-      </c>
-      <c r="G67">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6ARHM - Estadisticos 20222.xlsx
+++ b/grupos/6ARHM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="163">
   <si>
     <t>Materia</t>
   </si>
@@ -996,7 +996,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -1050,7 +1050,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -1073,7 +1073,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -1127,7 +1127,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1150,7 +1150,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>9</v>
@@ -1204,7 +1204,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1227,7 +1227,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -1281,7 +1281,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1304,7 +1304,7 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1381,7 +1381,7 @@
         <v>10</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -1435,7 +1435,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1458,7 +1458,7 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>10</v>
@@ -1512,7 +1512,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>10</v>
@@ -1535,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1589,7 +1589,7 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1612,7 +1612,7 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -1666,7 +1666,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1689,7 +1689,7 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>9</v>
@@ -1743,7 +1743,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1766,7 +1766,7 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D14">
         <v>10</v>
@@ -1820,7 +1820,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1843,7 +1843,7 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>9</v>
@@ -1897,7 +1897,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -1920,7 +1920,7 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1974,7 +1974,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -1997,7 +1997,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -2051,7 +2051,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -2074,7 +2074,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D18">
         <v>9</v>
@@ -2128,7 +2128,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -2151,7 +2151,7 @@
         <v>10</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>10</v>
@@ -2205,7 +2205,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -2228,7 +2228,7 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -2282,7 +2282,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2305,7 +2305,7 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -2359,7 +2359,7 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2382,7 +2382,7 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D22">
         <v>10</v>
@@ -2436,7 +2436,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2459,7 +2459,7 @@
         <v>10</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D23">
         <v>10</v>
@@ -2513,7 +2513,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2536,7 +2536,7 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D24">
         <v>9</v>
@@ -2590,7 +2590,7 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -2613,7 +2613,7 @@
         <v>10</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D25">
         <v>10</v>
@@ -2667,7 +2667,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2690,7 +2690,7 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D26">
         <v>9</v>
@@ -2744,7 +2744,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -2767,7 +2767,7 @@
         <v>7</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>10</v>
@@ -2821,7 +2821,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2844,7 +2844,7 @@
         <v>8</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D28">
         <v>9</v>
@@ -2898,7 +2898,7 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -2921,7 +2921,7 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2975,7 +2975,7 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2998,7 +2998,7 @@
         <v>9</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>9</v>
@@ -3052,7 +3052,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -3075,7 +3075,7 @@
         <v>10</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D31">
         <v>9</v>
@@ -3129,7 +3129,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3152,7 +3152,7 @@
         <v>10</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D32">
         <v>10</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3229,7 +3229,7 @@
         <v>9</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D33">
         <v>10</v>
@@ -3283,7 +3283,7 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3306,7 +3306,7 @@
         <v>8</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D34">
         <v>10</v>
@@ -3360,7 +3360,7 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -3383,7 +3383,7 @@
         <v>9</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <v>9</v>
@@ -3437,7 +3437,7 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>9</v>
@@ -3460,7 +3460,7 @@
         <v>10</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D36">
         <v>10</v>
@@ -3514,7 +3514,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>10</v>
@@ -3537,7 +3537,7 @@
         <v>9</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D37">
         <v>10</v>
@@ -3591,7 +3591,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>10</v>
@@ -3614,7 +3614,7 @@
         <v>10</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D38">
         <v>9</v>
@@ -3668,7 +3668,7 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
         <v>9</v>
@@ -3691,7 +3691,7 @@
         <v>9</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D39">
         <v>9</v>
@@ -3745,7 +3745,7 @@
         <v>9</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>9</v>
@@ -3878,7 +3878,7 @@
         <v>105</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>132</v>
@@ -3937,7 +3937,7 @@
         <v>105</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>132</v>
@@ -3996,7 +3996,7 @@
         <v>105</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>132</v>
@@ -4055,7 +4055,7 @@
         <v>105</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>132</v>
@@ -4114,7 +4114,7 @@
         <v>105</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>132</v>
@@ -4173,7 +4173,7 @@
         <v>105</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>132</v>
@@ -4232,7 +4232,7 @@
         <v>105</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>132</v>
@@ -4291,7 +4291,7 @@
         <v>105</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>132</v>
@@ -4350,7 +4350,7 @@
         <v>105</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>132</v>
@@ -4409,7 +4409,7 @@
         <v>105</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>132</v>
@@ -4468,7 +4468,7 @@
         <v>105</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>132</v>
@@ -4527,7 +4527,7 @@
         <v>105</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>132</v>
@@ -4586,7 +4586,7 @@
         <v>105</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>132</v>
@@ -4645,7 +4645,7 @@
         <v>105</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>132</v>
@@ -4704,7 +4704,7 @@
         <v>105</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>132</v>
@@ -4763,7 +4763,7 @@
         <v>105</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>132</v>
@@ -4822,7 +4822,7 @@
         <v>105</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>132</v>
@@ -4881,7 +4881,7 @@
         <v>105</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>128</v>
@@ -4940,7 +4940,7 @@
         <v>105</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>132</v>
@@ -4999,7 +4999,7 @@
         <v>105</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>132</v>
@@ -5058,7 +5058,7 @@
         <v>105</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>132</v>
@@ -5117,7 +5117,7 @@
         <v>105</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>132</v>
@@ -5176,7 +5176,7 @@
         <v>105</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>132</v>
@@ -5235,7 +5235,7 @@
         <v>105</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>132</v>
@@ -5294,7 +5294,7 @@
         <v>105</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>132</v>
@@ -5353,7 +5353,7 @@
         <v>105</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>132</v>
@@ -5412,7 +5412,7 @@
         <v>105</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>132</v>
@@ -5471,7 +5471,7 @@
         <v>105</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>132</v>
@@ -5530,7 +5530,7 @@
         <v>105</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>132</v>
@@ -5589,7 +5589,7 @@
         <v>105</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>132</v>
@@ -5648,7 +5648,7 @@
         <v>105</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>132</v>
@@ -5707,7 +5707,7 @@
         <v>105</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>132</v>
@@ -5766,7 +5766,7 @@
         <v>105</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>132</v>
@@ -5825,7 +5825,7 @@
         <v>105</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>132</v>
@@ -5884,7 +5884,7 @@
         <v>105</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>124</v>
@@ -5943,7 +5943,7 @@
         <v>105</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>132</v>
@@ -6046,7 +6046,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -6055,48 +6055,51 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>16.67</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3">
         <v>36</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>83.33</v>
+        <v>94.44</v>
       </c>
       <c r="G3">
-        <v>16.67</v>
+        <v>5.56</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6107,28 +6110,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4">
         <v>36</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="G4">
-        <v>5.56</v>
+        <v>2.78</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6139,28 +6142,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>97.22</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6171,7 +6174,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -6203,10 +6206,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>36</v>
@@ -6224,7 +6227,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6240,7 +6243,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6265,726 +6268,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920368</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920156</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920157</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920158</v>
-      </c>
-      <c r="B5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920369</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920160</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920161</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920162</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920163</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920164</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920370</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920372</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" t="s">
-        <v>138</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920165</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" t="s">
-        <v>139</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920167</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D15" t="s">
-        <v>140</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920166</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920371</v>
-      </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" t="s">
-        <v>142</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920171</v>
-      </c>
-      <c r="B18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18" t="s">
-        <v>143</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920172</v>
-      </c>
-      <c r="B19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920173</v>
-      </c>
-      <c r="B20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" t="s">
-        <v>145</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920174</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" t="s">
-        <v>146</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920306</v>
-      </c>
-      <c r="B22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" t="s">
-        <v>147</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920177</v>
-      </c>
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" t="s">
-        <v>148</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920178</v>
-      </c>
-      <c r="B24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920179</v>
-      </c>
-      <c r="B25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" t="s">
-        <v>150</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920180</v>
-      </c>
-      <c r="B26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" t="s">
-        <v>151</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920373</v>
-      </c>
-      <c r="B27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" t="s">
-        <v>71</v>
-      </c>
-      <c r="D27" t="s">
-        <v>152</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920145</v>
-      </c>
-      <c r="B28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" t="s">
-        <v>153</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920254</v>
-      </c>
-      <c r="B29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" t="s">
-        <v>120</v>
-      </c>
-      <c r="D29" t="s">
-        <v>154</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920181</v>
-      </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>115</v>
-      </c>
-      <c r="D30" t="s">
-        <v>155</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920393</v>
-      </c>
-      <c r="B31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920182</v>
-      </c>
-      <c r="B32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" t="s">
-        <v>157</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920183</v>
-      </c>
-      <c r="B33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" t="s">
-        <v>158</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920184</v>
-      </c>
-      <c r="B34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920154</v>
-      </c>
-      <c r="B35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" t="s">
-        <v>160</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920186</v>
-      </c>
-      <c r="B36" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" t="s">
-        <v>161</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920388</v>
-      </c>
-      <c r="B37" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" t="s">
-        <v>162</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -7032,7 +6315,7 @@
         <v>127</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7049,7 +6332,7 @@
         <v>128</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7066,7 +6349,7 @@
         <v>129</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7083,7 +6366,7 @@
         <v>130</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7100,7 +6383,7 @@
         <v>131</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7117,7 +6400,7 @@
         <v>132</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7134,7 +6417,7 @@
         <v>133</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7151,7 +6434,7 @@
         <v>134</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7168,7 +6451,7 @@
         <v>135</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7185,7 +6468,7 @@
         <v>136</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7202,7 +6485,7 @@
         <v>137</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7219,7 +6502,7 @@
         <v>138</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7236,7 +6519,7 @@
         <v>139</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7253,7 +6536,7 @@
         <v>140</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7270,7 +6553,7 @@
         <v>141</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7287,7 +6570,7 @@
         <v>142</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7304,7 +6587,7 @@
         <v>143</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7321,7 +6604,7 @@
         <v>144</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7338,7 +6621,7 @@
         <v>145</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7355,7 +6638,7 @@
         <v>146</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7372,7 +6655,7 @@
         <v>147</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7389,7 +6672,7 @@
         <v>148</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7406,7 +6689,7 @@
         <v>149</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7423,7 +6706,7 @@
         <v>150</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7440,7 +6723,7 @@
         <v>151</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7457,7 +6740,7 @@
         <v>152</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7474,7 +6757,7 @@
         <v>153</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7491,7 +6774,7 @@
         <v>154</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7508,7 +6791,7 @@
         <v>155</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7525,7 +6808,7 @@
         <v>156</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7542,7 +6825,7 @@
         <v>157</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7559,7 +6842,7 @@
         <v>158</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7576,7 +6859,7 @@
         <v>159</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -7593,7 +6876,7 @@
         <v>160</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -7610,7 +6893,7 @@
         <v>161</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -7627,7 +6910,7 @@
         <v>162</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7637,7 +6920,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7669,39 +6952,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920157</v>
+        <v>20330051920172</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920157</v>
+        <v>20330051920172</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7715,45 +6998,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920162</v>
+        <v>20330051920174</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>60</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920162</v>
+        <v>20330051920174</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7761,45 +7044,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920182</v>
+        <v>20330051920178</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>60</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920182</v>
+        <v>20330051920178</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7807,692 +7090,71 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920368</v>
+        <v>20330051920157</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>60</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920156</v>
+        <v>20330051920162</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>60</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920158</v>
+        <v>20330051920182</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>60</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920369</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920160</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920161</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" t="s">
-        <v>133</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920163</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920164</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920370</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920372</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920165</v>
-      </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920167</v>
-      </c>
-      <c r="B19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920166</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920371</v>
-      </c>
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920171</v>
-      </c>
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920173</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920306</v>
-      </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920177</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25" t="s">
-        <v>148</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920179</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26" t="s">
-        <v>150</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920180</v>
-      </c>
-      <c r="B27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" t="s">
-        <v>151</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920373</v>
-      </c>
-      <c r="B28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" t="s">
-        <v>152</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920145</v>
-      </c>
-      <c r="B29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" t="s">
-        <v>153</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920254</v>
-      </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" t="s">
-        <v>154</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920181</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>115</v>
-      </c>
-      <c r="D31" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920393</v>
-      </c>
-      <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" t="s">
-        <v>156</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>60</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920183</v>
-      </c>
-      <c r="B33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" t="s">
-        <v>158</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>20330051920184</v>
-      </c>
-      <c r="B34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920154</v>
-      </c>
-      <c r="B35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" t="s">
-        <v>160</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>60</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>20330051920186</v>
-      </c>
-      <c r="B36" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" t="s">
-        <v>161</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>60</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>20330051920388</v>
-      </c>
-      <c r="B37" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" t="s">
-        <v>162</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ARHM - Estadisticos 20222.xlsx
+++ b/grupos/6ARHM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -201,7 +201,7 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>Ochoa Martínez Mayeli</t>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>NC</t>
@@ -6209,7 +6212,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C7">
         <v>36</v>
@@ -6252,16 +6255,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6286,16 +6289,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>58</v>
@@ -6306,13 +6309,13 @@
         <v>20330051920368</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6323,13 +6326,13 @@
         <v>20330051920156</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6340,13 +6343,13 @@
         <v>20330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6357,13 +6360,13 @@
         <v>20330051920158</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6374,13 +6377,13 @@
         <v>20330051920369</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6391,13 +6394,13 @@
         <v>20330051920160</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6408,13 +6411,13 @@
         <v>20330051920161</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6425,13 +6428,13 @@
         <v>20330051920162</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6442,13 +6445,13 @@
         <v>20330051920163</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6459,13 +6462,13 @@
         <v>20330051920164</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6476,13 +6479,13 @@
         <v>20330051920370</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6493,13 +6496,13 @@
         <v>20330051920372</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6510,13 +6513,13 @@
         <v>20330051920165</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6527,13 +6530,13 @@
         <v>20330051920167</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6544,13 +6547,13 @@
         <v>20330051920166</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6561,13 +6564,13 @@
         <v>20330051920371</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6578,13 +6581,13 @@
         <v>20330051920171</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6595,13 +6598,13 @@
         <v>20330051920172</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6612,13 +6615,13 @@
         <v>20330051920173</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6629,13 +6632,13 @@
         <v>20330051920174</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6646,13 +6649,13 @@
         <v>20330051920306</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6663,13 +6666,13 @@
         <v>20330051920177</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6680,13 +6683,13 @@
         <v>20330051920178</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6697,13 +6700,13 @@
         <v>20330051920179</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6714,13 +6717,13 @@
         <v>20330051920180</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6731,13 +6734,13 @@
         <v>20330051920373</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6748,13 +6751,13 @@
         <v>20330051920145</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6765,13 +6768,13 @@
         <v>20330051920254</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6782,13 +6785,13 @@
         <v>20330051920181</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6799,13 +6802,13 @@
         <v>20330051920393</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6816,13 +6819,13 @@
         <v>20330051920182</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6833,13 +6836,13 @@
         <v>20330051920183</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6850,13 +6853,13 @@
         <v>20330051920184</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -6867,13 +6870,13 @@
         <v>20330051920154</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -6884,13 +6887,13 @@
         <v>20330051920186</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -6901,13 +6904,13 @@
         <v>20330051920388</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D37" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -6929,16 +6932,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6955,13 +6958,13 @@
         <v>20330051920172</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6978,13 +6981,13 @@
         <v>20330051920172</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7001,13 +7004,13 @@
         <v>20330051920174</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -7024,13 +7027,13 @@
         <v>20330051920174</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -7047,13 +7050,13 @@
         <v>20330051920178</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -7070,13 +7073,13 @@
         <v>20330051920178</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -7093,13 +7096,13 @@
         <v>20330051920157</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -7116,13 +7119,13 @@
         <v>20330051920162</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -7139,13 +7142,13 @@
         <v>20330051920182</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>

--- a/grupos/6ARHM - Estadisticos 20222.xlsx
+++ b/grupos/6ARHM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="78">
   <si>
     <t>Materia</t>
   </si>
@@ -201,12 +200,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
@@ -228,295 +227,40 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>CANSECO</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>VICTORIANO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>LUIS YAEL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>ADRIANA ARELY</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>MARIA YAZMIN</t>
-  </si>
-  <si>
-    <t>JAEL SAMAI</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA RUBI</t>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
   </si>
   <si>
     <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>IDETH JOSELYN</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>ESTHER ARISBETH</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
-    <t>EDGAR RAMSES</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>IRIS VIANNEY</t>
-  </si>
-  <si>
-    <t>MONSERRATH YARETZY</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>EVELYN IVETH</t>
-  </si>
-  <si>
-    <t>MARIAN</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>AYARI</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -569,11 +313,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1020,16 +765,16 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1097,16 +842,16 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1136,7 +881,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -1174,16 +919,16 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1213,13 +958,13 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1251,16 +996,16 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1290,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -1328,16 +1073,16 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1367,13 +1112,13 @@
         <v>9</v>
       </c>
       <c r="W8">
+        <v>8</v>
+      </c>
+      <c r="X8">
+        <v>9</v>
+      </c>
+      <c r="Y8">
         <v>7</v>
-      </c>
-      <c r="X8">
-        <v>9</v>
-      </c>
-      <c r="Y8">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1405,16 +1150,16 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1444,7 +1189,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1482,16 +1227,16 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1527,7 +1272,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1559,16 +1304,16 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1598,13 +1343,13 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1636,16 +1381,16 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1713,16 +1458,16 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1758,7 +1503,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1790,16 +1535,16 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1835,7 +1580,7 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1867,16 +1612,16 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1903,16 +1648,16 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>10</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1944,16 +1689,16 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1983,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -2021,16 +1766,16 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2098,16 +1843,16 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2137,7 +1882,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2175,16 +1920,16 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2252,16 +1997,16 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2329,16 +2074,16 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2368,13 +2113,13 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2406,16 +2151,16 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2445,7 +2190,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2483,16 +2228,16 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2560,16 +2305,16 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2637,16 +2382,16 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2682,7 +2427,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2714,16 +2459,16 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2750,13 +2495,13 @@
         <v>8</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>5</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2791,16 +2536,16 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2830,7 +2575,7 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2868,16 +2613,16 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2913,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2945,16 +2690,16 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2984,7 +2729,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3022,16 +2767,16 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3058,16 +2803,16 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3099,16 +2844,16 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3144,7 +2889,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3176,16 +2921,16 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3221,7 +2966,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3253,16 +2998,16 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3292,13 +3037,13 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3330,16 +3075,16 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3369,13 +3114,13 @@
         <v>10</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3407,16 +3152,16 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3452,7 +3197,7 @@
         <v>9</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3484,16 +3229,16 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3561,16 +3306,16 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3600,7 +3345,7 @@
         <v>10</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3638,16 +3383,16 @@
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3677,7 +3422,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>9</v>
@@ -3715,16 +3460,16 @@
         <v>-1</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3751,13 +3496,13 @@
         <v>10</v>
       </c>
       <c r="V39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y39">
         <v>7</v>
@@ -3902,16 +3647,16 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3961,16 +3706,16 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -4020,16 +3765,16 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -4079,16 +3824,16 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -4138,16 +3883,16 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -4197,16 +3942,16 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -4256,16 +4001,16 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -4315,16 +4060,16 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4374,16 +4119,16 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4433,16 +4178,16 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4492,16 +4237,16 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4551,16 +4296,16 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4610,16 +4355,16 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4669,16 +4414,16 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4728,16 +4473,16 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4787,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4846,16 +4591,16 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4905,16 +4650,16 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4964,16 +4709,16 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -5023,16 +4768,16 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -5082,16 +4827,16 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -5141,16 +4886,16 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -5200,16 +4945,16 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -5259,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -5318,16 +5063,16 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5377,16 +5122,16 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5436,16 +5181,16 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5495,16 +5240,16 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5554,16 +5299,16 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5613,16 +5358,16 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5672,16 +5417,16 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5731,16 +5476,16 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5790,16 +5535,16 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -5849,16 +5594,16 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -5908,16 +5653,16 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -5967,16 +5712,16 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -6013,6 +5758,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -6049,7 +5796,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -6058,30 +5805,30 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>6</v>
-      </c>
-      <c r="F2">
-        <v>83.33</v>
-      </c>
-      <c r="G2">
-        <v>16.67</v>
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="G2" s="2">
+        <v>5.6</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -6095,19 +5842,19 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>94.44</v>
-      </c>
-      <c r="G3">
-        <v>5.56</v>
+      <c r="F3" s="2">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="G3" s="2">
+        <v>5.6</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6127,11 +5874,11 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4">
-        <v>97.22</v>
-      </c>
-      <c r="G4">
-        <v>2.78</v>
+      <c r="F4" s="2">
+        <v>97.2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2.8</v>
       </c>
       <c r="H4">
         <v>9.1</v>
@@ -6139,7 +5886,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6159,19 +5906,19 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="2">
+        <v>100</v>
+      </c>
+      <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6191,19 +5938,19 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6223,10 +5970,10 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
@@ -6235,7 +5982,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6280,650 +6027,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20330051920368</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20330051920156</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>20330051920157</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920158</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>20330051920369</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>20330051920160</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>20330051920161</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>20330051920162</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920163</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>20330051920164</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>20330051920370</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>20330051920372</v>
-      </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>20330051920165</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" t="s">
-        <v>140</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920167</v>
-      </c>
-      <c r="B15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" t="s">
-        <v>141</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>20330051920166</v>
-      </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" t="s">
-        <v>113</v>
-      </c>
-      <c r="D16" t="s">
-        <v>142</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>20330051920371</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>114</v>
-      </c>
-      <c r="D17" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>20330051920171</v>
-      </c>
-      <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" t="s">
-        <v>144</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920172</v>
-      </c>
-      <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>20330051920173</v>
-      </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" t="s">
-        <v>146</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>20330051920174</v>
-      </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" t="s">
-        <v>147</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>20330051920306</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>20330051920177</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" t="s">
-        <v>149</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>20330051920178</v>
-      </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24" t="s">
-        <v>150</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>20330051920179</v>
-      </c>
-      <c r="B25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" t="s">
-        <v>151</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>20330051920180</v>
-      </c>
-      <c r="B26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" t="s">
-        <v>152</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>20330051920373</v>
-      </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" t="s">
-        <v>153</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>20330051920145</v>
-      </c>
-      <c r="B28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" t="s">
-        <v>154</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>20330051920254</v>
-      </c>
-      <c r="B29" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" t="s">
-        <v>155</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>20330051920181</v>
-      </c>
-      <c r="B30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" t="s">
-        <v>156</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>20330051920393</v>
-      </c>
-      <c r="B31" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" t="s">
-        <v>157</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>20330051920182</v>
-      </c>
-      <c r="B32" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" t="s">
-        <v>158</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>20330051920183</v>
-      </c>
-      <c r="B33" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" t="s">
-        <v>159</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>20330051920184</v>
-      </c>
-      <c r="B34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" t="s">
-        <v>125</v>
-      </c>
-      <c r="D34" t="s">
-        <v>160</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>20330051920154</v>
-      </c>
-      <c r="B35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" t="s">
-        <v>161</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>20330051920186</v>
-      </c>
-      <c r="B36" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" t="s">
-        <v>126</v>
-      </c>
-      <c r="D36" t="s">
-        <v>162</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>20330051920388</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" t="s">
-        <v>127</v>
-      </c>
-      <c r="D37" t="s">
-        <v>163</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6955,22 +6059,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920172</v>
+        <v>20330051920174</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" t="s">
         <v>75</v>
       </c>
-      <c r="D2" t="s">
-        <v>145</v>
-      </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6978,19 +6082,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920172</v>
+        <v>20330051920174</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
         <v>75</v>
       </c>
-      <c r="D3" t="s">
-        <v>145</v>
-      </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>60</v>
@@ -7001,22 +6105,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920174</v>
+        <v>20330051920178</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7024,22 +6128,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920174</v>
+        <v>20330051920178</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7047,116 +6151,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920178</v>
+        <v>20330051920172</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920178</v>
-      </c>
-      <c r="B7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920157</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920162</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920182</v>
-      </c>
-      <c r="B10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ARHM - Estadisticos 20222.xlsx
+++ b/grupos/6ARHM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="75">
   <si>
     <t>Materia</t>
   </si>
@@ -203,18 +203,18 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -233,25 +233,16 @@
     <t>QUIRIZ</t>
   </si>
   <si>
-    <t>MATA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
     <t>LUZ ESTRELLA</t>
   </si>
   <si>
     <t>MONICA</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
   </si>
 </sst>
 </file>
@@ -759,7 +750,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -836,7 +827,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -913,7 +904,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -949,7 +940,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -990,7 +981,7 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1067,7 +1058,7 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1103,7 +1094,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1144,7 +1135,7 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1221,7 +1212,7 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1257,7 +1248,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1298,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1334,7 +1325,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1375,7 +1366,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1452,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1488,7 +1479,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>9</v>
@@ -1529,7 +1520,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1606,7 +1597,7 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1642,7 +1633,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1683,7 +1674,7 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1760,7 +1751,7 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -1796,7 +1787,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -1837,7 +1828,7 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -1914,7 +1905,7 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -1991,7 +1982,7 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2068,7 +2059,7 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2104,7 +2095,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>6</v>
@@ -2145,7 +2136,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2222,7 +2213,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2231,7 +2222,7 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2258,7 +2249,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2267,7 +2258,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2299,7 +2290,7 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2376,7 +2367,7 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2453,7 +2444,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2462,7 +2453,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -2489,7 +2480,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2498,7 +2489,7 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2530,7 +2521,7 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2566,7 +2557,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -2607,7 +2598,7 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2643,7 +2634,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -2684,7 +2675,7 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2720,7 +2711,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>10</v>
@@ -2761,7 +2752,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -2838,7 +2829,7 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -2847,7 +2838,7 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>9</v>
@@ -2915,7 +2906,7 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -2992,7 +2983,7 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3069,7 +3060,7 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3105,7 +3096,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>8</v>
@@ -3146,7 +3137,7 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3182,7 +3173,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -3223,7 +3214,7 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3300,7 +3291,7 @@
         <v>9</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3377,7 +3368,7 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3454,7 +3445,7 @@
         <v>7</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -3641,7 +3632,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3700,7 +3691,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3759,7 +3750,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3818,7 +3809,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3877,7 +3868,7 @@
         <v>76</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3936,7 +3927,7 @@
         <v>92</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -3995,7 +3986,7 @@
         <v>88</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4054,7 +4045,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4113,7 +4104,7 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4172,7 +4163,7 @@
         <v>80</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -4231,7 +4222,7 @@
         <v>96</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -4290,7 +4281,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -4349,7 +4340,7 @@
         <v>88</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -4408,7 +4399,7 @@
         <v>84</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -4467,7 +4458,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -4526,7 +4517,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -4585,7 +4576,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -4644,7 +4635,7 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -4703,7 +4694,7 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -4762,7 +4753,7 @@
         <v>80</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -4821,7 +4812,7 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -4880,7 +4871,7 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -4939,7 +4930,7 @@
         <v>60</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -4998,7 +4989,7 @@
         <v>80</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -5057,7 +5048,7 @@
         <v>76</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5116,7 +5107,7 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5175,7 +5166,7 @@
         <v>92</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5234,7 +5225,7 @@
         <v>92</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5293,7 +5284,7 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -5352,7 +5343,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5411,7 +5402,7 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5470,7 +5461,7 @@
         <v>72</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -5529,7 +5520,7 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -5588,7 +5579,7 @@
         <v>76</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -5647,7 +5638,7 @@
         <v>100</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -5706,7 +5697,7 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -5828,7 +5819,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -5837,19 +5828,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5860,28 +5851,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4">
         <v>36</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5892,10 +5883,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5">
         <v>36</v>
@@ -5913,7 +5904,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5924,7 +5915,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -5945,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5956,7 +5947,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -6027,7 +6018,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6065,16 +6056,16 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6082,16 +6073,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920174</v>
+        <v>20330051920178</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
         <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6100,75 +6091,6 @@
         <v>60</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920178</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920178</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920172</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ARHM - Estadisticos 20222.xlsx
+++ b/grupos/6ARHM - Estadisticos 20222.xlsx
@@ -753,7 +753,7 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>9</v>
@@ -907,7 +907,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -943,7 +943,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -984,7 +984,7 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>9</v>
@@ -1061,7 +1061,7 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -1138,7 +1138,7 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>9</v>
@@ -1215,7 +1215,7 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -1292,7 +1292,7 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -1328,7 +1328,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1369,7 +1369,7 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -1446,7 +1446,7 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -1523,7 +1523,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1600,7 +1600,7 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>10</v>
@@ -1636,7 +1636,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1677,7 +1677,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>10</v>
@@ -1754,7 +1754,7 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>10</v>
@@ -1831,7 +1831,7 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>9</v>
@@ -1908,7 +1908,7 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>10</v>
@@ -1985,7 +1985,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>10</v>
@@ -2062,7 +2062,7 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -2139,7 +2139,7 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
         <v>10</v>
@@ -2216,7 +2216,7 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>10</v>
@@ -2252,7 +2252,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2293,7 +2293,7 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>9</v>
@@ -2370,7 +2370,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>10</v>
@@ -2447,7 +2447,7 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>10</v>
@@ -2483,7 +2483,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2524,7 +2524,7 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>10</v>
@@ -2560,7 +2560,7 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2601,7 +2601,7 @@
         <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>9</v>
@@ -2678,7 +2678,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -2755,7 +2755,7 @@
         <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>10</v>
@@ -2832,7 +2832,7 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
         <v>9</v>
@@ -2909,7 +2909,7 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>10</v>
@@ -2986,7 +2986,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>10</v>
@@ -3063,7 +3063,7 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>10</v>
@@ -3140,7 +3140,7 @@
         <v>7</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
         <v>9</v>
@@ -3217,7 +3217,7 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
         <v>10</v>
@@ -3294,7 +3294,7 @@
         <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
         <v>10</v>
@@ -3371,7 +3371,7 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
         <v>9</v>
@@ -3448,7 +3448,7 @@
         <v>9</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J39">
         <v>10</v>
@@ -3635,7 +3635,7 @@
         <v>105</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>120</v>
@@ -3694,7 +3694,7 @@
         <v>105</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>120</v>
@@ -3753,7 +3753,7 @@
         <v>105</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>120</v>
@@ -3812,7 +3812,7 @@
         <v>105</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>120</v>
@@ -3871,7 +3871,7 @@
         <v>105</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>120</v>
@@ -3930,7 +3930,7 @@
         <v>105</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>120</v>
@@ -3989,7 +3989,7 @@
         <v>105</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>120</v>
@@ -4048,7 +4048,7 @@
         <v>105</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>120</v>
@@ -4107,7 +4107,7 @@
         <v>105</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>120</v>
@@ -4166,7 +4166,7 @@
         <v>105</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>120</v>
@@ -4225,7 +4225,7 @@
         <v>105</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>120</v>
@@ -4284,7 +4284,7 @@
         <v>105</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>120</v>
@@ -4343,7 +4343,7 @@
         <v>105</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>120</v>
@@ -4402,7 +4402,7 @@
         <v>105</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
         <v>120</v>
@@ -4461,7 +4461,7 @@
         <v>105</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>120</v>
@@ -4520,7 +4520,7 @@
         <v>105</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>120</v>
@@ -4579,7 +4579,7 @@
         <v>105</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
         <v>120</v>
@@ -4638,7 +4638,7 @@
         <v>105</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>120</v>
@@ -4697,7 +4697,7 @@
         <v>105</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>120</v>
@@ -4756,7 +4756,7 @@
         <v>105</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>120</v>
@@ -4815,7 +4815,7 @@
         <v>105</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>120</v>
@@ -4874,7 +4874,7 @@
         <v>105</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>120</v>
@@ -4933,7 +4933,7 @@
         <v>105</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J26">
         <v>120</v>
@@ -4992,7 +4992,7 @@
         <v>105</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>120</v>
@@ -5051,7 +5051,7 @@
         <v>105</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
         <v>120</v>
@@ -5110,7 +5110,7 @@
         <v>105</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
         <v>120</v>
@@ -5169,7 +5169,7 @@
         <v>105</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>120</v>
@@ -5228,7 +5228,7 @@
         <v>105</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>120</v>
@@ -5287,7 +5287,7 @@
         <v>105</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
         <v>120</v>
@@ -5346,7 +5346,7 @@
         <v>105</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>120</v>
@@ -5405,7 +5405,7 @@
         <v>105</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34">
         <v>120</v>
@@ -5464,7 +5464,7 @@
         <v>105</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35">
         <v>120</v>
@@ -5523,7 +5523,7 @@
         <v>105</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36">
         <v>120</v>
@@ -5582,7 +5582,7 @@
         <v>105</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37">
         <v>120</v>
@@ -5641,7 +5641,7 @@
         <v>105</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38">
         <v>120</v>
@@ -5700,7 +5700,7 @@
         <v>105</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J39">
         <v>120</v>

--- a/grupos/6ARHM - Estadisticos 20222.xlsx
+++ b/grupos/6ARHM - Estadisticos 20222.xlsx
@@ -3614,58 +3614,58 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>100</v>
       </c>
       <c r="F4">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>100</v>
       </c>
       <c r="J4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M4">
         <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3673,58 +3673,58 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
       </c>
       <c r="D5">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>100</v>
       </c>
       <c r="F5">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>100</v>
       </c>
       <c r="J5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3732,58 +3732,58 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
       <c r="D6">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>88</v>
       </c>
       <c r="F6">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>100</v>
       </c>
       <c r="H6">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>100</v>
       </c>
       <c r="J6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="L6">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M6">
         <v>100</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3791,58 +3791,58 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
       </c>
       <c r="D7">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
       </c>
       <c r="F7">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>100</v>
       </c>
       <c r="J7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3850,58 +3850,58 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
       <c r="D8">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>100</v>
       </c>
       <c r="F8">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>76</v>
       </c>
       <c r="H8">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>100</v>
       </c>
       <c r="J8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3909,58 +3909,58 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>100</v>
       </c>
       <c r="F9">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>92</v>
       </c>
       <c r="H9">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I9">
         <v>100</v>
       </c>
       <c r="J9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3968,58 +3968,58 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="D10">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>100</v>
       </c>
       <c r="F10">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>88</v>
       </c>
       <c r="H10">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>100</v>
       </c>
       <c r="J10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4027,58 +4027,58 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
       </c>
       <c r="F11">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>100</v>
       </c>
       <c r="H11">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>100</v>
       </c>
       <c r="J11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4086,58 +4086,58 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>100</v>
       </c>
       <c r="D12">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>100</v>
       </c>
       <c r="F12">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>100</v>
       </c>
       <c r="H12">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>100</v>
       </c>
       <c r="J12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4145,58 +4145,58 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
       </c>
       <c r="D13">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>100</v>
       </c>
       <c r="F13">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>80</v>
       </c>
       <c r="H13">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>100</v>
       </c>
       <c r="J13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>80</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4204,58 +4204,58 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>100</v>
       </c>
       <c r="F14">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>96</v>
       </c>
       <c r="H14">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>100</v>
       </c>
       <c r="J14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4263,58 +4263,58 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>100</v>
       </c>
       <c r="D15">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>100</v>
       </c>
       <c r="F15">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>100</v>
       </c>
       <c r="H15">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>100</v>
       </c>
       <c r="J15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>100</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4322,58 +4322,58 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>100</v>
       </c>
       <c r="D16">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>100</v>
       </c>
       <c r="F16">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>88</v>
       </c>
       <c r="H16">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I16">
         <v>100</v>
       </c>
       <c r="J16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4381,58 +4381,58 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>100</v>
       </c>
       <c r="D17">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>100</v>
       </c>
       <c r="F17">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>84</v>
       </c>
       <c r="H17">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M17">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4440,58 +4440,58 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>100</v>
       </c>
       <c r="D18">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>100</v>
       </c>
       <c r="F18">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>100</v>
       </c>
       <c r="H18">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>100</v>
       </c>
       <c r="J18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4499,58 +4499,58 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
       </c>
       <c r="D19">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>100</v>
       </c>
       <c r="F19">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>100</v>
       </c>
       <c r="H19">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I19">
         <v>100</v>
       </c>
       <c r="J19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4558,58 +4558,58 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>100</v>
       </c>
       <c r="D20">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>100</v>
       </c>
       <c r="F20">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>100</v>
       </c>
       <c r="H20">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I20">
         <v>100</v>
       </c>
       <c r="J20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4617,58 +4617,58 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>100</v>
       </c>
       <c r="D21">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="E21">
         <v>88</v>
       </c>
       <c r="F21">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="G21">
         <v>100</v>
       </c>
       <c r="H21">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>100</v>
       </c>
       <c r="J21">
-        <v>120</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="L21">
-        <v>124</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="M21">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4676,58 +4676,58 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
       </c>
       <c r="D22">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>100</v>
       </c>
       <c r="F22">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>100</v>
       </c>
       <c r="H22">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>100</v>
       </c>
       <c r="J22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4735,58 +4735,58 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>100</v>
       </c>
       <c r="D23">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>92</v>
       </c>
       <c r="F23">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>80</v>
       </c>
       <c r="H23">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L23">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4794,58 +4794,58 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>100</v>
       </c>
       <c r="D24">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>100</v>
       </c>
       <c r="F24">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>100</v>
       </c>
       <c r="H24">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I24">
         <v>100</v>
       </c>
       <c r="J24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4853,58 +4853,58 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
       </c>
       <c r="D25">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>100</v>
       </c>
       <c r="F25">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>100</v>
       </c>
       <c r="H25">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>100</v>
       </c>
       <c r="J25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4912,58 +4912,58 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
       </c>
       <c r="F26">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>60</v>
       </c>
       <c r="H26">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4971,58 +4971,58 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>100</v>
       </c>
       <c r="D27">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>100</v>
       </c>
       <c r="F27">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>80</v>
       </c>
       <c r="H27">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>100</v>
       </c>
       <c r="J27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5030,58 +5030,58 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
       </c>
       <c r="D28">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
       </c>
       <c r="F28">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>76</v>
       </c>
       <c r="H28">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>100</v>
       </c>
       <c r="J28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>76</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5089,58 +5089,58 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
       </c>
       <c r="D29">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>100</v>
       </c>
       <c r="F29">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>100</v>
       </c>
       <c r="H29">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>100</v>
       </c>
       <c r="J29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5148,58 +5148,58 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C30">
         <v>100</v>
       </c>
       <c r="D30">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
       </c>
       <c r="F30">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>92</v>
       </c>
       <c r="H30">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>100</v>
       </c>
       <c r="J30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5207,58 +5207,58 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>100</v>
       </c>
       <c r="D31">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>100</v>
       </c>
       <c r="F31">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>92</v>
       </c>
       <c r="H31">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>100</v>
       </c>
       <c r="J31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5266,58 +5266,58 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
       </c>
       <c r="D32">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>100</v>
       </c>
       <c r="F32">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>100</v>
       </c>
       <c r="H32">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I32">
         <v>100</v>
       </c>
       <c r="J32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>100</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5325,58 +5325,58 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>100</v>
       </c>
       <c r="D33">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>100</v>
       </c>
       <c r="F33">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>100</v>
       </c>
       <c r="H33">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I33">
         <v>100</v>
       </c>
       <c r="J33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M33">
         <v>100</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5384,58 +5384,58 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
       </c>
       <c r="D34">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>100</v>
       </c>
       <c r="F34">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>100</v>
       </c>
       <c r="H34">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I34">
         <v>100</v>
       </c>
       <c r="J34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M34">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5443,58 +5443,58 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C35">
         <v>100</v>
       </c>
       <c r="D35">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E35">
         <v>100</v>
       </c>
       <c r="F35">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>72</v>
       </c>
       <c r="H35">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I35">
         <v>100</v>
       </c>
       <c r="J35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M35">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5502,58 +5502,58 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C36">
         <v>100</v>
       </c>
       <c r="D36">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>100</v>
       </c>
       <c r="F36">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G36">
         <v>100</v>
       </c>
       <c r="H36">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I36">
         <v>100</v>
       </c>
       <c r="J36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K36">
         <v>100</v>
       </c>
       <c r="L36">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M36">
         <v>100</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5561,58 +5561,58 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>100</v>
       </c>
       <c r="D37">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E37">
         <v>100</v>
       </c>
       <c r="F37">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>76</v>
       </c>
       <c r="H37">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I37">
         <v>100</v>
       </c>
       <c r="J37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K37">
         <v>100</v>
       </c>
       <c r="L37">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M37">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5620,58 +5620,58 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C38">
         <v>100</v>
       </c>
       <c r="D38">
-        <v>124</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="E38">
         <v>100</v>
       </c>
       <c r="F38">
-        <v>124</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G38">
         <v>100</v>
       </c>
       <c r="H38">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I38">
         <v>100</v>
       </c>
       <c r="J38">
-        <v>120</v>
+        <v>96.8</v>
       </c>
       <c r="K38">
         <v>100</v>
       </c>
       <c r="L38">
-        <v>124</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M38">
         <v>100</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5679,58 +5679,58 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C39">
         <v>100</v>
       </c>
       <c r="D39">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E39">
         <v>100</v>
       </c>
       <c r="F39">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G39">
         <v>100</v>
       </c>
       <c r="H39">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I39">
         <v>100</v>
       </c>
       <c r="J39">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K39">
         <v>100</v>
       </c>
       <c r="L39">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M39">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ARHM - Estadisticos 20222.xlsx
+++ b/grupos/6ARHM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="69">
   <si>
     <t>Materia</t>
   </si>
@@ -200,12 +200,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -225,24 +225,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
   </si>
 </sst>
 </file>
@@ -768,22 +750,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -845,22 +827,22 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -922,28 +904,28 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -955,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -999,22 +981,22 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1076,25 +1058,25 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1109,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1153,22 +1135,22 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1230,22 +1212,22 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1307,25 +1289,25 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1384,22 +1366,22 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1461,22 +1443,22 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1488,13 +1470,13 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1538,22 +1520,22 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1615,25 +1597,25 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1692,22 +1674,22 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1769,34 +1751,34 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>10</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -1846,25 +1828,25 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -1923,22 +1905,22 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2000,22 +1982,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2077,25 +2059,25 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>6</v>
@@ -2154,22 +2136,22 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2187,7 +2169,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2231,25 +2213,25 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2258,13 +2240,13 @@
         <v>10</v>
       </c>
       <c r="W23">
+        <v>7</v>
+      </c>
+      <c r="X23">
+        <v>10</v>
+      </c>
+      <c r="Y23">
         <v>6</v>
-      </c>
-      <c r="X23">
-        <v>10</v>
-      </c>
-      <c r="Y23">
-        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2308,22 +2290,22 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2335,7 +2317,7 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2385,22 +2367,22 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2462,40 +2444,40 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U26">
+        <v>6</v>
+      </c>
+      <c r="V26">
+        <v>10</v>
+      </c>
+      <c r="W26">
         <v>7</v>
       </c>
-      <c r="V26">
-        <v>10</v>
-      </c>
-      <c r="W26">
+      <c r="X26">
+        <v>10</v>
+      </c>
+      <c r="Y26">
         <v>6</v>
-      </c>
-      <c r="X26">
-        <v>10</v>
-      </c>
-      <c r="Y26">
-        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2539,22 +2521,22 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2563,13 +2545,13 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2616,28 +2598,28 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>7</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -2693,22 +2675,22 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2770,37 +2752,37 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>9</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>10</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -2847,22 +2829,22 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2924,22 +2906,22 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3001,25 +2983,25 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>9</v>
@@ -3028,13 +3010,13 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3078,34 +3060,34 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>10</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3155,22 +3137,22 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>8</v>
@@ -3188,7 +3170,7 @@
         <v>9</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3232,22 +3214,22 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3309,22 +3291,22 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>9</v>
@@ -3333,13 +3315,13 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>9</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>9</v>
@@ -3386,25 +3368,25 @@
         <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U38">
         <v>10</v>
@@ -3463,40 +3445,40 @@
         <v>7</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>10</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3724,7 +3706,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>98</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3777,7 +3759,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3901,7 +3883,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3960,7 +3942,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>96</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4019,7 +4001,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>90</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4137,7 +4119,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4196,7 +4178,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>80</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4255,7 +4237,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4373,7 +4355,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4432,7 +4414,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>88</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4659,16 +4641,16 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>98.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="Q21">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="R21">
-        <v>98.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="S21">
-        <v>98</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4727,7 +4709,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>94</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4780,13 +4762,13 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>72</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4845,7 +4827,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4904,7 +4886,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4951,7 +4933,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4963,7 +4945,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5022,7 +5004,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5081,7 +5063,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>76</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5199,7 +5181,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>96</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5258,7 +5240,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>96</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5435,7 +5417,7 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5494,7 +5476,7 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>74</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5603,7 +5585,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -5612,7 +5594,7 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5662,13 +5644,13 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>96.8</v>
+        <v>97.5</v>
       </c>
       <c r="Q38">
         <v>100</v>
       </c>
       <c r="R38">
-        <v>96.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -5730,7 +5712,7 @@
         <v>100</v>
       </c>
       <c r="S39">
-        <v>92</v>
+        <v>94.7</v>
       </c>
     </row>
   </sheetData>
@@ -5787,7 +5769,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -5796,19 +5778,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5819,10 +5801,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3">
         <v>36</v>
@@ -5840,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5851,7 +5833,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -5872,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5904,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5936,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5968,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6018,7 +6000,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6048,52 +6030,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920174</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920178</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
